--- a/generated/spreadsheet/verbose/householder-planning-application-hh-verbose.xlsx
+++ b/generated/spreadsheet/verbose/householder-planning-application-hh-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N106"/>
+  <dimension ref="A1:N105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -642,12 +642,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>application-sub-type</t>
+          <t>planning-authority</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Application sub type</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -656,7 +656,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Further classification of the application type for specific variations within the main application type</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -690,12 +690,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>planning-authority</t>
+          <t>submission-date</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Submission date</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -704,12 +704,12 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>Date the application is submitted in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>submission-date</t>
+          <t>modules</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Modules[]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -752,12 +752,12 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>List of required modules for this application that can be used to validate the application</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -786,21 +786,29 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+          <t>Documents[]</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -844,19 +852,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>name</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -900,19 +908,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>description</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -922,7 +930,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -956,29 +964,29 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>document-types</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1012,24 +1020,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>document-types</t>
+          <t>uploaded-date</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Uploaded date</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1068,29 +1076,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>uploaded-date</t>
+          <t>file</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>base64-content</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Base64</t>
+        </is>
+      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1150,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>base64-content</t>
+          <t>filename</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Base64</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1154,7 +1170,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1198,17 +1214,17 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>filename</t>
+          <t>mime-type</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1218,7 +1234,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1262,22 +1278,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>mime-type</t>
+          <t>file-size</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>File size</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1306,37 +1322,29 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>fee</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
+          <t>Fee</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>file-size</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>File size</t>
-        </is>
-      </c>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1346,7 +1354,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1380,19 +1388,19 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>amount-paid</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1436,99 +1444,83 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>amount-paid</t>
+          <t>transactions</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Transactions[]</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Access and rights of way</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>access-rights-of-way</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>new-altered-vehicle</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>fee</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Fee</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>transactions</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Transactions[]</t>
-        </is>
-      </c>
+          <t>New or altered vehicle access</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Access and rights of way</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>access-rights-of-way</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
@@ -1536,12 +1528,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>new-altered-vehicle</t>
+          <t>new-altered-pedestrian</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>New or altered vehicle access</t>
+          <t>New or altered pedestrian access</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
@@ -1552,7 +1544,7 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
+          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -1576,12 +1568,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>new-altered-pedestrian</t>
+          <t>change-right-of-way</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>New or altered pedestrian access</t>
+          <t>Change to right of way</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
@@ -1592,7 +1584,7 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
+          <t>Will the proposal change public rights of way (diversion/extinguishment/creation)</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1616,28 +1608,36 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>change-right-of-way</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Change to right of way</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Will the proposal change public rights of way (diversion/extinguishment/creation)</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -1647,40 +1647,40 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>agent-contact</t>
+        </is>
+      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>agent-reference</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -1695,16 +1695,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>agent-contact</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1712,23 +1704,31 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>agent-reference</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -1762,21 +1762,29 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -1786,7 +1794,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1820,24 +1828,24 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>contact-priority</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -1847,8 +1855,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n"/>
-      <c r="B27" s="2" t="n"/>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>agent-details</t>
+        </is>
+      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1856,63 +1872,47 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>contact-priority</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>agent-details</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="n"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1930,21 +1930,29 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -1954,7 +1962,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1988,19 +1996,19 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2010,7 +2018,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2044,19 +2052,19 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -2100,19 +2108,19 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -2156,19 +2164,19 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2178,7 +2186,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2202,29 +2210,21 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>user-role</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>User role</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
@@ -2272,12 +2272,12 @@
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2287,64 +2287,56 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="2" t="n"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information if an agent is being used.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>user-role</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>User role</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -2352,23 +2344,31 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -2402,21 +2402,29 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2426,7 +2434,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2460,24 +2468,24 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>contact-priority</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -2487,72 +2495,64 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n"/>
-      <c r="B39" s="2" t="n"/>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Name and contact information for the parties making the application.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicants</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Applicants[]</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>contact-priority</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="n"/>
+      <c r="B40" s="2" t="n"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2570,21 +2570,29 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -2594,7 +2602,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2628,19 +2636,19 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -2650,7 +2658,7 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2684,19 +2692,19 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -2740,19 +2748,19 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -2796,19 +2804,19 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -2818,90 +2826,82 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n"/>
-      <c r="B45" s="2" t="n"/>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity net gain</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>bng</t>
+        </is>
+      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>bng-exempt</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Biodiversity gain exemption</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Statement whether the biodiversity gain condition will apply if permission is granted. Householder applicants need to confirm the biodiversity gain condition does not apply.</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>bng</t>
+          <t>checklist</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>bng-exempt</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain exemption</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
@@ -2912,12 +2912,12 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Statement whether the biodiversity gain condition will apply if permission is granted. Householder applicants need to confirm the biodiversity gain condition does not apply.</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -2929,27 +2929,27 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Conflict of interest</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>checklist</t>
+          <t>conflict-of-interest</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>national-req-types</t>
+          <t>conflict-to-declare</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -2960,12 +2960,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -2975,16 +2975,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>conflict-of-interest</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
@@ -2992,12 +2984,12 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>conflict-to-declare</t>
+          <t>conflict-person-name</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Conflict person name</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -3008,17 +3000,17 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3032,12 +3024,12 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>conflict-person-name</t>
+          <t>conflict-details</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
@@ -3048,7 +3040,7 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -3063,21 +3055,29 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="2" t="n"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>conflict-details</t>
+          <t>name</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
@@ -3088,7 +3088,7 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>A name of a person</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -3098,21 +3098,13 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>declaration</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -3120,12 +3112,12 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
@@ -3136,12 +3128,12 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -3160,12 +3152,12 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
@@ -3176,12 +3168,12 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -3191,37 +3183,53 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n"/>
-      <c r="B53" s="2" t="n"/>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>What materials are being used for the proposed development</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>building-elements</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr"/>
+          <t>Building elements[]</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>building-element-type</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Building element type</t>
+        </is>
+      </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -3231,16 +3239,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>materials</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="n"/>
+      <c r="B54" s="2" t="n"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>What materials are being used for the proposed development</t>
@@ -3258,12 +3258,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>building-element-type</t>
+          <t>existing-materials</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Building element type</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -3272,17 +3272,17 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3306,12 +3306,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>existing-materials</t>
+          <t>proposed-materials</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Existing materials</t>
+          <t>Proposed materials</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -3320,7 +3320,7 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -3354,12 +3354,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>proposed-materials</t>
+          <t>materials-not-applicable</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Materials not applicable</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -3368,12 +3368,12 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>Indicates this building element is not relevant to the application</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>materials-not-applicable</t>
+          <t>materials-not-known</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Materials not applicable</t>
+          <t>Materials not known</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -3416,7 +3416,7 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Indicates this building element is not relevant to the application</t>
+          <t>Indicates the materials for this building element are not yet known</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -3440,31 +3440,23 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>building-elements</t>
+          <t>providing-additional-material-information</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>materials-not-known</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Materials not known</t>
-        </is>
-      </c>
+          <t>Providing additional material information</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Indicates the materials for this building element are not yet known</t>
+          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -3474,7 +3466,7 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3488,28 +3480,36 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>providing-additional-material-information</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Providing additional material information</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -3519,45 +3519,45 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n"/>
-      <c r="B60" s="2" t="n"/>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>ownership-certs</t>
+        </is>
+      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>What materials are being used for the proposed development</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>sole-owner</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -3567,16 +3567,8 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>ownership-certs</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="n"/>
+      <c r="B61" s="2" t="n"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
@@ -3584,12 +3576,12 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>sole-owner</t>
+          <t>agricultural-tenants</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
+          <t>Agricultural tenants</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
@@ -3600,7 +3592,7 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -3624,33 +3616,49 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>agricultural-tenants</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3684,19 +3692,19 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -3706,7 +3714,7 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3740,19 +3748,19 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -3796,19 +3804,19 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -3852,19 +3860,19 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -3874,7 +3882,7 @@
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3898,34 +3906,26 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>notice-date</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Notice date</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -3944,36 +3944,28 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>owners-and-tenants</t>
+          <t>steps-taken</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>notice-date</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Notice date</t>
-        </is>
-      </c>
+          <t>Steps taken</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -3992,23 +3984,31 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>steps-taken</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>newspaper-name</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="H69" s="2" t="inlineStr"/>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4042,12 +4042,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>newspaper-name</t>
+          <t>publication-date</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Publication date</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -4056,12 +4056,12 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -4080,41 +4080,33 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>ownership-cert-option</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>publication-date</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4128,12 +4120,12 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>ownership-cert-option</t>
+          <t>applicant-signature</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
+          <t>Applicant signature</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
@@ -4144,12 +4136,12 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Digital signature of the applicant</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -4168,12 +4160,12 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>applicant-signature</t>
+          <t>agent-signature</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Applicant signature</t>
+          <t>Agent signature</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
@@ -4184,7 +4176,7 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the applicant</t>
+          <t>Digital signature of the agent (if applicable)</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -4208,12 +4200,12 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>agent-signature</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Agent signature</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
@@ -4224,7 +4216,7 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the agent (if applicable)</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -4239,21 +4231,29 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n"/>
-      <c r="B75" s="2" t="n"/>
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Parking arrangements</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>parking</t>
+        </is>
+      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Details of any changes the proposed development would make to parking facilities.</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>is-existing-parking-affected</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Existing parking affected</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
@@ -4264,31 +4264,23 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Will the proposed works affect existing car parking arrangements</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Parking arrangements</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>parking</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="n"/>
+      <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>Details of any changes the proposed development would make to parking facilities.</t>
@@ -4296,12 +4288,12 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>is-existing-parking-affected</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Existing parking affected</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
@@ -4312,36 +4304,44 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Will the proposed works affect existing car parking arrangements</t>
+          <t>A description of how the proposed works will affect existing car parking arrangements</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n"/>
-      <c r="B77" s="2" t="n"/>
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Details of any changes the proposed development would make to parking facilities.</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
@@ -4352,31 +4352,23 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>A description of how the proposed works will affect existing car parking arrangements</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -4384,12 +4376,12 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
@@ -4400,17 +4392,17 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4424,12 +4416,12 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
@@ -4440,7 +4432,7 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -4464,12 +4456,12 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
@@ -4480,7 +4472,7 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -4504,12 +4496,12 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
@@ -4520,7 +4512,7 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -4535,21 +4527,29 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n"/>
-      <c r="B82" s="2" t="n"/>
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>proposal-details</t>
+        </is>
+      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>proposal-description</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
@@ -4560,7 +4560,7 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -4570,21 +4570,13 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>proposal-details</t>
-        </is>
-      </c>
+      <c r="A83" s="2" t="n"/>
+      <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>What development, works or change of use is proposed</t>
@@ -4592,12 +4584,12 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>proposal-description</t>
+          <t>proposal-started</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
@@ -4608,12 +4600,12 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -4632,12 +4624,12 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>proposal-started</t>
+          <t>proposal-started-date</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
@@ -4648,17 +4640,17 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4672,12 +4664,12 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>proposal-started-date</t>
+          <t>proposal-completed</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
@@ -4688,17 +4680,17 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4704,12 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed</t>
+          <t>proposal-completed-date</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal completion date</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
@@ -4728,52 +4720,68 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n"/>
-      <c r="B87" s="2" t="n"/>
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed-date</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr"/>
-      <c r="G87" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>site-boundary</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Site boundary</t>
+        </is>
+      </c>
       <c r="H87" s="2" t="inlineStr"/>
       <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -4783,16 +4791,8 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="n"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>site-boundary</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr"/>
@@ -4824,12 +4824,12 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr"/>
@@ -4872,7 +4872,7 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -4906,12 +4906,12 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr"/>
@@ -4920,12 +4920,12 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>northing</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr"/>
@@ -4968,7 +4968,7 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr"/>
@@ -5016,7 +5016,7 @@
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -5050,12 +5050,12 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr"/>
@@ -5064,7 +5064,7 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr"/>
@@ -5112,12 +5112,12 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>uprns</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr"/>
@@ -5160,7 +5160,7 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -5175,64 +5175,56 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n"/>
-      <c r="B96" s="2" t="n"/>
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>uprns</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A97" s="2" t="n"/>
+      <c r="B97" s="2" t="n"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -5240,12 +5232,12 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
@@ -5256,12 +5248,12 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -5280,12 +5272,12 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr"/>
@@ -5296,17 +5288,17 @@
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5320,23 +5312,31 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>other-contact</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr"/>
-      <c r="G99" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>fullname</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5370,12 +5370,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>fullname</t>
+          <t>number</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
@@ -5384,7 +5384,7 @@
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
@@ -5418,12 +5418,12 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
@@ -5432,7 +5432,7 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
@@ -5447,45 +5447,45 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n"/>
-      <c r="B102" s="2" t="n"/>
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Trees and hedges information</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>trees-hedges</t>
+        </is>
+      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>has-falling-trees-risk</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Falling trees risk</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr"/>
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Whether there are falling trees on-premises or adjacent premises that are a risk to the development</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -5495,16 +5495,8 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>Trees and hedges information</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>trees-hedges</t>
-        </is>
-      </c>
+      <c r="A103" s="2" t="n"/>
+      <c r="B103" s="2" t="n"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>Details of trees and/or hedges that will be affected by the proposed development</t>
@@ -5512,28 +5504,36 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>has-falling-trees-risk</t>
+          <t>falling-trees-document</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Falling trees risk</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr"/>
-      <c r="G103" s="2" t="inlineStr"/>
+          <t>Falling trees document</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H103" s="2" t="inlineStr"/>
       <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>Whether there are falling trees on-premises or adjacent premises that are a risk to the development</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -5552,36 +5552,28 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>falling-trees-document</t>
+          <t>tree-removal</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Falling trees document</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Tree removal</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr"/>
       <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Whether trees or hedges need to be pruned or removed</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -5600,79 +5592,39 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>tree-removal</t>
+          <t>tree-removal-plan</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Tree removal</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr"/>
-      <c r="G105" s="2" t="inlineStr"/>
+          <t>Tree removal plan</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H105" s="2" t="inlineStr"/>
       <c r="I105" s="2" t="inlineStr"/>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges need to be pruned or removed</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="n"/>
-      <c r="B106" s="2" t="n"/>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>tree-removal-plan</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>Tree removal plan</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr"/>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-      <c r="K106" s="2" t="inlineStr"/>
-      <c r="L106" s="2" t="inlineStr">
-        <is>
-          <t>A unique reference for the data item</t>
-        </is>
-      </c>
-      <c r="M106" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N106" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -5680,42 +5632,42 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A36:A39"/>
-    <mergeCell ref="A40:A45"/>
-    <mergeCell ref="B97:B102"/>
-    <mergeCell ref="B78:B82"/>
-    <mergeCell ref="B88:B96"/>
-    <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A103:A106"/>
-    <mergeCell ref="A61:A75"/>
-    <mergeCell ref="B61:B75"/>
-    <mergeCell ref="B83:B87"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="A83:A87"/>
-    <mergeCell ref="B47"/>
+    <mergeCell ref="B82:B86"/>
+    <mergeCell ref="A39:A44"/>
+    <mergeCell ref="A60:A74"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="B102:B105"/>
+    <mergeCell ref="B45"/>
+    <mergeCell ref="B53:B59"/>
+    <mergeCell ref="B2:B18"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="B96:B101"/>
+    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="B87:B95"/>
+    <mergeCell ref="B39:B44"/>
+    <mergeCell ref="B60:B74"/>
+    <mergeCell ref="B47:B49"/>
     <mergeCell ref="B46"/>
-    <mergeCell ref="B103:B106"/>
-    <mergeCell ref="B54:B60"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B24:B27"/>
-    <mergeCell ref="B28:B35"/>
-    <mergeCell ref="A54:A60"/>
+    <mergeCell ref="A77:A81"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="B27:B34"/>
+    <mergeCell ref="A45"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="A2:A18"/>
+    <mergeCell ref="A82:A86"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A27:A34"/>
     <mergeCell ref="A46"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="B36:B39"/>
-    <mergeCell ref="A97:A102"/>
-    <mergeCell ref="B40:B45"/>
-    <mergeCell ref="A78:A82"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A88:A96"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B2:B19"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A28:A35"/>
-    <mergeCell ref="A47"/>
+    <mergeCell ref="A102:A105"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="B77:B81"/>
+    <mergeCell ref="A96:A101"/>
+    <mergeCell ref="A87:A95"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="B35:B38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/verbose/householder-planning-application-hh-verbose.xlsx
+++ b/generated/spreadsheet/verbose/householder-planning-application-hh-verbose.xlsx
@@ -3173,7 +3173,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>proposal-description</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">

--- a/generated/spreadsheet/verbose/householder-planning-application-hh-verbose.xlsx
+++ b/generated/spreadsheet/verbose/householder-planning-application-hh-verbose.xlsx
@@ -435,8 +435,8 @@
     <col width="72" customWidth="1" min="3" max="3"/>
     <col width="43" customWidth="1" min="4" max="4"/>
     <col width="43" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
@@ -3200,36 +3200,28 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>building-elements</t>
+          <t>proposal-material-details</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>building-element-type</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Building element type</t>
-        </is>
-      </c>
+          <t>Proposal material details</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Whether the proposal involves material details that need to be provided</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -3258,12 +3250,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>existing-materials</t>
+          <t>building-element-type</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Existing materials</t>
+          <t>Building element type</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -3272,17 +3264,17 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3306,12 +3298,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>proposed-materials</t>
+          <t>existing-materials</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -3320,7 +3312,7 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -3354,12 +3346,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>materials-not-applicable</t>
+          <t>proposed-materials</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Materials not applicable</t>
+          <t>Proposed materials</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -3368,12 +3360,12 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Indicates this building element is not relevant to the application</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">

--- a/generated/spreadsheet/verbose/householder-planning-application-hh-verbose.xlsx
+++ b/generated/spreadsheet/verbose/householder-planning-application-hh-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N105"/>
+  <dimension ref="A1:N106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -442,7 +442,7 @@
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="72" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -521,37 +521,37 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>submission-reference</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Submission reference</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -560,7 +560,7 @@
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A unique reference for the submission</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -579,17 +579,17 @@
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -627,27 +627,27 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>planning-authority</t>
+          <t>specification-profile</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Specification profile</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -656,7 +656,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>The specification profile used to determine context-specific allowed codelist values for the application</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -675,27 +675,27 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>submission-date</t>
+          <t>planning-authority</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -704,12 +704,12 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -723,27 +723,27 @@
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>submitted-at</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
+          <t>Submitted at</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -752,12 +752,12 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>The date and time the application was submitted</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -771,49 +771,41 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>created-at</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Created at</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The date and time the submission payload was created</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -827,17 +819,17 @@
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -852,19 +844,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -883,17 +875,17 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -908,19 +900,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>name</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -930,7 +922,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -939,17 +931,17 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -964,29 +956,29 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>document-types</t>
+          <t>description</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -995,17 +987,17 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1020,24 +1012,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>uploaded-date</t>
+          <t>document-types</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1051,17 +1043,17 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1076,37 +1068,29 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>uploaded-date</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>base64-content</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Base64</t>
-        </is>
-      </c>
+          <t>Uploaded date</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1115,17 +1099,17 @@
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1150,17 +1134,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>filename</t>
+          <t>base64-content</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>Base64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1170,7 +1154,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1179,17 +1163,17 @@
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1214,17 +1198,17 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>mime-type</t>
+          <t>filename</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1234,7 +1218,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1227,17 @@
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1278,22 +1262,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>file-size</t>
+          <t>mime-type</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>File size</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1307,54 +1291,62 @@
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>fee</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Fee</t>
+          <t>Documents[]</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>file</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>file-size</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>File size</t>
+        </is>
+      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1363,17 +1355,17 @@
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1388,24 +1380,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>amount-paid</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1419,17 +1411,17 @@
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1444,83 +1436,99 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>transactions</t>
+          <t>amount-paid</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Transactions[]</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Access and rights of way</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>access-rights-of-way</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>new-altered-vehicle</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>New or altered vehicle access</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
+          <t>Submission details</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>fee</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Fee</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>transactions</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Transactions[]</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Access and rights of way</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>access-rights-of-way</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
@@ -1528,12 +1536,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>new-altered-pedestrian</t>
+          <t>new-altered-vehicle</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>New or altered pedestrian access</t>
+          <t>New or altered vehicle access</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
@@ -1544,7 +1552,7 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
+          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -1568,12 +1576,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>change-right-of-way</t>
+          <t>new-altered-pedestrian</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Change to right of way</t>
+          <t>New or altered pedestrian access</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
@@ -1584,7 +1592,7 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Will the proposal change public rights of way (diversion/extinguishment/creation)</t>
+          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1608,36 +1616,28 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>change-right-of-way</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Change to right of way</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Will the proposal change public rights of way (diversion/extinguishment/creation)</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -1647,40 +1647,40 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>agent-contact</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information if an agent is being used.</t>
+          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>agent-reference</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -1695,8 +1695,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n"/>
-      <c r="B24" s="2" t="n"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>agent-contact</t>
+        </is>
+      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1704,31 +1712,23 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>agent-reference</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1762,29 +1762,21 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -1794,7 +1786,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1828,24 +1820,24 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -1855,16 +1847,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>agent-details</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="n"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1872,47 +1856,63 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n"/>
-      <c r="B28" s="2" t="n"/>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>agent-details</t>
+        </is>
+      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1930,29 +1930,21 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -1962,7 +1954,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1996,19 +1988,19 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2018,7 +2010,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2052,19 +2044,19 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -2108,19 +2100,19 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -2164,19 +2156,19 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2186,7 +2178,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2210,21 +2202,29 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>user-role</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
@@ -2272,12 +2272,12 @@
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2287,56 +2287,64 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>user-role</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n"/>
-      <c r="B36" s="2" t="n"/>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -2344,31 +2352,23 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -2402,29 +2402,21 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2434,7 +2426,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2468,24 +2460,24 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -2495,64 +2487,72 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="2" t="n"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n"/>
-      <c r="B40" s="2" t="n"/>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2570,29 +2570,21 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -2602,7 +2594,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2636,19 +2628,19 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -2658,7 +2650,7 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2692,19 +2684,19 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -2748,19 +2740,19 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -2804,19 +2796,19 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -2826,82 +2818,90 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity net gain</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>bng</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
+          <t>Name and contact information for the parties making the application.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>bng-exempt</t>
+          <t>applicants</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain exemption</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Statement whether the biodiversity gain condition will apply if permission is granted. Householder applicants need to confirm the biodiversity gain condition does not apply.</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Biodiversity net gain</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>checklist</t>
+          <t>bng</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>national-req-types</t>
+          <t>bng-exempt</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Biodiversity gain exemption</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
@@ -2912,12 +2912,12 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Statement whether the biodiversity gain condition will apply if permission is granted. Householder applicants need to confirm the biodiversity gain condition does not apply.</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -2929,27 +2929,27 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Conflict of interest</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>conflict-of-interest</t>
+          <t>checklist</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>conflict-to-declare</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -2960,12 +2960,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -2975,8 +2975,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="2" t="n"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>conflict-of-interest</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
@@ -2984,12 +2992,12 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>conflict-person-name</t>
+          <t>conflict-to-declare</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -3000,17 +3008,17 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3024,12 +3032,12 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>conflict-details</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
@@ -3040,7 +3048,7 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -3055,29 +3063,21 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>declaration</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>conflict-details</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
@@ -3088,7 +3088,7 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -3098,13 +3098,21 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n"/>
-      <c r="B51" s="2" t="n"/>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -3112,12 +3120,12 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
@@ -3128,12 +3136,12 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -3152,12 +3160,12 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
@@ -3168,12 +3176,12 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -3183,29 +3191,21 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>materials</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="n"/>
+      <c r="B53" s="2" t="n"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>What materials are being used for the proposed development</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>proposal-material-details</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Proposal material details</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
@@ -3216,12 +3216,12 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves material details that need to be provided</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -3231,8 +3231,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n"/>
-      <c r="B54" s="2" t="n"/>
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>What materials are being used for the proposed development</t>
@@ -3240,36 +3248,28 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>building-elements</t>
+          <t>proposal-material-details</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>building-element-type</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Building element type</t>
-        </is>
-      </c>
+          <t>Proposal material details</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Whether the proposal involves material details that need to be provided</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>existing-materials</t>
+          <t>building-element-type</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Existing materials</t>
+          <t>Building element type</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -3312,17 +3312,17 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3346,12 +3346,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>proposed-materials</t>
+          <t>existing-materials</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -3360,7 +3360,7 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>materials-not-known</t>
+          <t>proposed-materials</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Materials not known</t>
+          <t>Proposed materials</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -3408,12 +3408,12 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Indicates the materials for this building element are not yet known</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -3432,23 +3432,31 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>providing-additional-material-information</t>
+          <t>building-elements</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Providing additional material information</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr"/>
+          <t>Building elements[]</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>materials-not-known</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Materials not known</t>
+        </is>
+      </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
+          <t>Indicates the materials for this building element are not yet known</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -3458,7 +3466,7 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3472,36 +3480,28 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>providing-additional-material-information</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Providing additional material information</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -3511,45 +3511,45 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>ownership-certs</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>What materials are being used for the proposed development</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>sole-owner</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -3559,8 +3559,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n"/>
-      <c r="B61" s="2" t="n"/>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>ownership-certs</t>
+        </is>
+      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
@@ -3568,12 +3576,12 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>agricultural-tenants</t>
+          <t>sole-owner</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
+          <t>Sole owner</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
@@ -3584,7 +3592,7 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -3608,49 +3616,33 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>owners-and-tenants</t>
+          <t>agricultural-tenants</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Agricultural tenants</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3684,19 +3676,19 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -3706,7 +3698,7 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3740,19 +3732,19 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -3796,19 +3788,19 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -3852,19 +3844,19 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -3874,7 +3866,7 @@
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3898,26 +3890,34 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>notice-date</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Notice date</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -3936,28 +3936,36 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>steps-taken</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>notice-served-date</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Notice served date</t>
+        </is>
+      </c>
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -3976,41 +3984,33 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>ownership-cert-option</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>newspaper-name</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>Newspaper name</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr"/>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4024,41 +4024,33 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>steps-taken</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>publication-date</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Steps taken</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4072,33 +4064,41 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>ownership-cert-option</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>newspaper-name</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4112,33 +4112,41 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>applicant-signature</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Applicant signature</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>publication-date</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the applicant</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4152,12 +4160,12 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>agent-signature</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Agent signature</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
@@ -4168,7 +4176,7 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the agent (if applicable)</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -4178,7 +4186,7 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4192,12 +4200,12 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
@@ -4208,44 +4216,36 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>Parking arrangements</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>parking</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="n"/>
+      <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Details of any changes the proposed development would make to parking facilities.</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>is-existing-parking-affected</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Existing parking affected</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
@@ -4256,12 +4256,12 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Will the proposed works affect existing car parking arrangements</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -4271,8 +4271,16 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n"/>
-      <c r="B76" s="2" t="n"/>
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Parking arrangements</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>parking</t>
+        </is>
+      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>Details of any changes the proposed development would make to parking facilities.</t>
@@ -4280,12 +4288,12 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>is-existing-parking-affected</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Existing parking affected</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
@@ -4296,44 +4304,36 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>A description of how the proposed works will affect existing car parking arrangements</t>
+          <t>Will the proposed works affect existing car parking arrangements</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Details of any changes the proposed development would make to parking facilities.</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
@@ -4344,23 +4344,31 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>A description of how the proposed works will affect existing car parking arrangements</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n"/>
-      <c r="B78" s="2" t="n"/>
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -4368,12 +4376,12 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
@@ -4384,17 +4392,17 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4408,12 +4416,12 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
@@ -4424,7 +4432,7 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -4448,12 +4456,12 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
@@ -4464,12 +4472,12 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -4488,12 +4496,12 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
@@ -4504,12 +4512,12 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -4519,29 +4527,21 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>proposal-details</t>
-        </is>
-      </c>
+      <c r="A82" s="2" t="n"/>
+      <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
@@ -4552,7 +4552,7 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -4562,13 +4562,21 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n"/>
-      <c r="B83" s="2" t="n"/>
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>proposal-details</t>
+        </is>
+      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>What development, works or change of use is proposed</t>
@@ -4576,12 +4584,12 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>proposal-started</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
@@ -4592,12 +4600,12 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -4616,12 +4624,12 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>proposal-started-date</t>
+          <t>proposal-started</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
@@ -4632,17 +4640,17 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4656,12 +4664,12 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed</t>
+          <t>proposal-started-date</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
@@ -4672,17 +4680,17 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4696,12 +4704,12 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed-date</t>
+          <t>proposal-completed</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
@@ -4712,68 +4720,52 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A87" s="2" t="n"/>
+      <c r="B87" s="2" t="n"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>proposal-completed-date</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>site-boundary</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>Site boundary</t>
-        </is>
-      </c>
+          <t>Proposal completion date</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr"/>
       <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -4783,8 +4775,16 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n"/>
-      <c r="B88" s="2" t="n"/>
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -4802,12 +4802,12 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>site-boundary</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr"/>
@@ -4816,12 +4816,12 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -4850,12 +4850,12 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr"/>
@@ -4864,7 +4864,7 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr"/>
@@ -4912,12 +4912,12 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr"/>
@@ -4960,12 +4960,12 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -4994,12 +4994,12 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>northing</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr"/>
@@ -5008,12 +5008,12 @@
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -5042,12 +5042,12 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr"/>
@@ -5056,12 +5056,12 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr"/>
@@ -5104,12 +5104,12 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>uprns</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr"/>
@@ -5152,7 +5152,7 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>A text description providing details about the subject.</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -5167,56 +5167,64 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A96" s="2" t="n"/>
+      <c r="B96" s="2" t="n"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr"/>
-      <c r="G96" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>uprns</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n"/>
-      <c r="B97" s="2" t="n"/>
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -5224,12 +5232,12 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Site seen from public area</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
@@ -5240,12 +5248,12 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -5264,12 +5272,12 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr"/>
@@ -5280,17 +5288,17 @@
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5304,31 +5312,23 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>fullname</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5362,12 +5362,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>fullname</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Full name</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
@@ -5376,7 +5376,7 @@
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>number</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
@@ -5424,7 +5424,7 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
@@ -5439,45 +5439,45 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>Trees and hedges information</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>trees-hedges</t>
-        </is>
-      </c>
+      <c r="A102" s="2" t="n"/>
+      <c r="B102" s="2" t="n"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>has-falling-trees-risk</t>
+          <t>other-contact</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Falling trees risk</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr"/>
-      <c r="G102" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="H102" s="2" t="inlineStr"/>
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>Whether there are falling trees on-premises or adjacent premises that are a risk to the development</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -5487,8 +5487,16 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n"/>
-      <c r="B103" s="2" t="n"/>
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Trees and hedges information</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>trees-hedges</t>
+        </is>
+      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>Details of trees and/or hedges that will be affected by the proposed development</t>
@@ -5496,36 +5504,28 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>falling-trees-document</t>
+          <t>has-falling-trees-risk</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Falling trees document</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Falling trees risk</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr"/>
       <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Whether there are falling trees on-premises or adjacent premises that are a risk to the development</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -5544,28 +5544,36 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>tree-removal</t>
+          <t>falling-trees-document</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Tree removal</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr"/>
-      <c r="G104" s="2" t="inlineStr"/>
+          <t>Falling trees document</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H104" s="2" t="inlineStr"/>
       <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges need to be pruned or removed</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -5584,39 +5592,79 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>tree-removal-plan</t>
+          <t>tree-removal</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Tree removal plan</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Tree removal</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr"/>
       <c r="I105" s="2" t="inlineStr"/>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
+          <t>Whether trees or hedges need to be pruned or removed</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n"/>
+      <c r="B106" s="2" t="n"/>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>tree-removal-plan</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Tree removal plan</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
           <t>A unique reference for the data item</t>
         </is>
       </c>
-      <c r="M105" s="2" t="inlineStr">
+      <c r="M106" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N105" s="2" t="inlineStr">
+      <c r="N106" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -5624,42 +5672,42 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="B82:B86"/>
-    <mergeCell ref="A39:A44"/>
-    <mergeCell ref="A60:A74"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="B102:B105"/>
-    <mergeCell ref="B45"/>
-    <mergeCell ref="B53:B59"/>
-    <mergeCell ref="B2:B18"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="B96:B101"/>
-    <mergeCell ref="B23:B26"/>
-    <mergeCell ref="B87:B95"/>
-    <mergeCell ref="B39:B44"/>
-    <mergeCell ref="B60:B74"/>
-    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="A36:A39"/>
+    <mergeCell ref="A40:A45"/>
+    <mergeCell ref="B97:B102"/>
+    <mergeCell ref="B78:B82"/>
+    <mergeCell ref="B88:B96"/>
+    <mergeCell ref="A2:A19"/>
+    <mergeCell ref="A103:A106"/>
+    <mergeCell ref="A61:A75"/>
+    <mergeCell ref="B61:B75"/>
+    <mergeCell ref="B83:B87"/>
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="A83:A87"/>
+    <mergeCell ref="B47"/>
     <mergeCell ref="B46"/>
-    <mergeCell ref="A77:A81"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="B27:B34"/>
-    <mergeCell ref="A45"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="A2:A18"/>
-    <mergeCell ref="A82:A86"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A27:A34"/>
+    <mergeCell ref="B103:B106"/>
+    <mergeCell ref="B54:B60"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B24:B27"/>
+    <mergeCell ref="B28:B35"/>
+    <mergeCell ref="A54:A60"/>
     <mergeCell ref="A46"/>
-    <mergeCell ref="A102:A105"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="B77:B81"/>
-    <mergeCell ref="A96:A101"/>
-    <mergeCell ref="A87:A95"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="B36:B39"/>
+    <mergeCell ref="A97:A102"/>
+    <mergeCell ref="B40:B45"/>
+    <mergeCell ref="A78:A82"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A88:A96"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="B2:B19"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A28:A35"/>
+    <mergeCell ref="A47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/verbose/householder-planning-application-hh-verbose.xlsx
+++ b/generated/spreadsheet/verbose/householder-planning-application-hh-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N106"/>
+  <dimension ref="A1:N109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -440,9 +440,9 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="72" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -2156,19 +2156,27 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>address-text</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>Address Text</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2212,19 +2220,27 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>postcode</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2258,21 +2274,37 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -2306,12 +2338,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>user-role</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
@@ -2320,12 +2352,12 @@
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -2335,56 +2367,64 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>user-role</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="n"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -2392,31 +2432,23 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2450,29 +2482,21 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2482,7 +2506,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2516,24 +2540,24 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -2543,64 +2567,72 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="n"/>
+      <c r="B40" s="2" t="n"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2618,29 +2650,21 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -2650,7 +2674,7 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2684,19 +2708,19 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -2706,7 +2730,7 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2740,19 +2764,19 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -2796,19 +2820,19 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -2852,115 +2876,155 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Text representation of an address or site</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>applicants</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>postcode</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>The postal code</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Postcode for a contact address or site</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity net gain</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>bng</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>bng-exempt</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity gain exemption</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>Statement whether the biodiversity gain condition will apply if permission is granted. Householder applicants need to confirm the biodiversity gain condition does not apply.</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>checklist</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>Name and contact information for the parties making the application.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>national-req-types</t>
+          <t>applicants</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-      <c r="K47" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -2970,34 +3034,34 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Conflict of interest</t>
+          <t>Biodiversity net gain</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>conflict-of-interest</t>
+          <t>bng</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>conflict-to-declare</t>
+          <t>bng-exempt</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Biodiversity gain exemption</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -3008,7 +3072,7 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Statement whether the biodiversity gain condition will apply if permission is granted. Householder applicants need to confirm the biodiversity gain condition does not apply.</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -3023,21 +3087,29 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n"/>
-      <c r="B49" s="2" t="n"/>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>checklist</t>
+        </is>
+      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>person-reference</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
@@ -3048,7 +3120,7 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Reference to the applicant or agent with the conflict</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -3058,13 +3130,21 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="2" t="n"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>conflict-of-interest</t>
+        </is>
+      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
@@ -3072,12 +3152,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>conflict-details</t>
+          <t>conflict-to-declare</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
@@ -3088,34 +3168,26 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>declaration</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3136,7 +3208,7 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -3146,7 +3218,7 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3155,17 +3227,17 @@
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>conflict-details</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
@@ -3176,23 +3248,31 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n"/>
-      <c r="B53" s="2" t="n"/>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -3200,12 +3280,12 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
@@ -3216,12 +3296,12 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -3231,29 +3311,21 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>materials</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="n"/>
+      <c r="B54" s="2" t="n"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>What materials are being used for the proposed development</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>proposal-material-details</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Proposal material details</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
@@ -3264,7 +3336,7 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves material details that need to be provided</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -3283,41 +3355,33 @@
       <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>What materials are being used for the proposed development</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>building-elements</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>building-element-type</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Building element type</t>
-        </is>
-      </c>
+          <t>Declaration date</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -3327,8 +3391,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n"/>
-      <c r="B56" s="2" t="n"/>
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>What materials are being used for the proposed development</t>
@@ -3336,41 +3408,33 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>building-elements</t>
+          <t>proposal-material-details</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>existing-materials</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Existing materials</t>
-        </is>
-      </c>
+          <t>Proposal material details</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>Whether the proposal involves material details that need to be provided</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3394,12 +3458,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>proposed-materials</t>
+          <t>building-element-type</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Building element type</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -3408,17 +3472,17 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3442,12 +3506,12 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>materials-not-known</t>
+          <t>existing-materials</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Materials not known</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -3456,12 +3520,12 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Indicates the materials for this building element are not yet known</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -3480,33 +3544,41 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>providing-additional-material-information</t>
+          <t>building-elements</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Providing additional material information</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr"/>
+          <t>Building elements[]</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>proposed-materials</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Proposed materials</t>
+        </is>
+      </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3520,22 +3592,22 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>building-elements</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
+          <t>Building elements[]</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>materials-not-known</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Materials not known</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
@@ -3544,44 +3616,36 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Indicates the materials for this building element are not yet known</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>ownership-certs</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="n"/>
+      <c r="B61" s="2" t="n"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>What materials are being used for the proposed development</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>sole-owner</t>
+          <t>providing-additional-material-information</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
+          <t>Providing additional material information</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
@@ -3592,7 +3656,7 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -3611,33 +3675,41 @@
       <c r="B62" s="2" t="n"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>What materials are being used for the proposed development</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>agricultural-tenants</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -3647,8 +3719,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n"/>
-      <c r="B63" s="2" t="n"/>
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>ownership-certs</t>
+        </is>
+      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
@@ -3656,49 +3736,33 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>owners-and-tenants</t>
+          <t>sole-owner</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3712,44 +3776,28 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>owners-and-tenants</t>
+          <t>agricultural-tenants</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>first-name</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
+          <t>Agricultural tenants</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -3788,19 +3836,19 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -3810,7 +3858,7 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3844,19 +3892,19 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -3900,19 +3948,19 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -3922,7 +3970,7 @@
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3946,31 +3994,47 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>notice-served-date</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Notice served date</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr"/>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-      <c r="K68" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3984,28 +4048,52 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>ownership-cert-option</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-      <c r="K69" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -4024,23 +4112,47 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>steps-taken</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-      <c r="K70" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -4064,22 +4176,22 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
+          <t>Owners and tenants[]</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>newspaper-name</t>
+          <t>notice-served-date</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Notice served date</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
@@ -4088,17 +4200,17 @@
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4112,41 +4224,33 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>ownership-cert-option</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>publication-date</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4160,12 +4264,12 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>person-reference</t>
+          <t>steps-taken</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Steps taken</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
@@ -4176,7 +4280,7 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -4186,7 +4290,7 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4200,28 +4304,36 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>newspaper-name</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -4240,23 +4352,31 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>publication-date</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -4271,29 +4391,21 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Parking arrangements</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>parking</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="n"/>
+      <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Details of any changes the proposed development would make to parking facilities.</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>is-existing-parking-affected</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Existing parking affected</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
@@ -4304,12 +4416,12 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Will the proposed works affect existing car parking arrangements</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -4323,17 +4435,17 @@
       <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Details of any changes the proposed development would make to parking facilities.</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
@@ -4344,44 +4456,36 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>A description of how the proposed works will affect existing car parking arrangements</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
@@ -4392,12 +4496,12 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -4407,21 +4511,29 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n"/>
-      <c r="B79" s="2" t="n"/>
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Parking arrangements</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>parking</t>
+        </is>
+      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Details of any changes the proposed development would make to parking facilities.</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>is-existing-parking-affected</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Existing parking affected</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
@@ -4432,17 +4544,17 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Will the proposed works affect existing car parking arrangements</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4451,17 +4563,17 @@
       <c r="B80" s="2" t="n"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Details of any changes the proposed development would make to parking facilities.</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
@@ -4472,7 +4584,7 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A description of how the proposed works will affect existing car parking arrangements</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -4487,8 +4599,16 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n"/>
-      <c r="B81" s="2" t="n"/>
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -4496,12 +4616,12 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
@@ -4512,17 +4632,17 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4536,12 +4656,12 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
@@ -4552,7 +4672,7 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -4567,29 +4687,21 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>proposal-details</t>
-        </is>
-      </c>
+      <c r="A83" s="2" t="n"/>
+      <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
@@ -4600,7 +4712,7 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -4610,7 +4722,7 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4619,17 +4731,17 @@
       <c r="B84" s="2" t="n"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>proposal-started</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
@@ -4640,17 +4752,17 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4659,17 +4771,17 @@
       <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>proposal-started-date</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
@@ -4680,12 +4792,12 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -4695,8 +4807,16 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n"/>
-      <c r="B86" s="2" t="n"/>
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>proposal-details</t>
+        </is>
+      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>What development, works or change of use is proposed</t>
@@ -4704,12 +4824,12 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
@@ -4720,12 +4840,12 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -4744,12 +4864,12 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed-date</t>
+          <t>proposal-started</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
@@ -4760,68 +4880,52 @@
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="n"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>proposal-started-date</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>site-boundary</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>Site boundary</t>
-        </is>
-      </c>
+          <t>Proposal start date</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -4835,46 +4939,38 @@
       <c r="B89" s="2" t="n"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>proposal-completed</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>address-text</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>Proposal completed</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr"/>
       <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4883,41 +4979,33 @@
       <c r="B90" s="2" t="n"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>proposal-completed-date</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Proposal completion date</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr"/>
       <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -4927,8 +5015,16 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n"/>
-      <c r="B91" s="2" t="n"/>
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -4946,12 +5042,12 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>geometry</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr"/>
@@ -4960,17 +5056,17 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4994,31 +5090,39 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr"/>
-      <c r="I92" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5042,26 +5146,34 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr"/>
-      <c r="I93" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -5090,26 +5202,34 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr"/>
-      <c r="I94" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>uprns</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -5138,21 +5258,29 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr"/>
-      <c r="I95" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>usrns</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject.</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -5186,12 +5314,12 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>uprns</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr"/>
@@ -5200,12 +5328,12 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -5215,50 +5343,50 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A97" s="2" t="n"/>
+      <c r="B97" s="2" t="n"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr"/>
-      <c r="G97" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>northing</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Northing</t>
+        </is>
+      </c>
       <c r="H97" s="2" t="inlineStr"/>
       <c r="I97" s="2" t="inlineStr"/>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5267,38 +5395,46 @@
       <c r="B98" s="2" t="n"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr"/>
-      <c r="G98" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
       <c r="H98" s="2" t="inlineStr"/>
       <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5307,33 +5443,41 @@
       <c r="B99" s="2" t="n"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr"/>
-      <c r="G99" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
       <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -5343,8 +5487,16 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n"/>
-      <c r="B100" s="2" t="n"/>
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -5352,36 +5504,28 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>fullname</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr"/>
       <c r="I100" s="2" t="inlineStr"/>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -5400,36 +5544,28 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Site visit contact type</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -5448,31 +5584,23 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr"/>
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
@@ -5482,50 +5610,50 @@
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>Trees and hedges information</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>trees-hedges</t>
-        </is>
-      </c>
+      <c r="A103" s="2" t="n"/>
+      <c r="B103" s="2" t="n"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>has-falling-trees-risk</t>
+          <t>other-contact</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Falling trees risk</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr"/>
-      <c r="G103" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>fullname</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="H103" s="2" t="inlineStr"/>
       <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>Whether there are falling trees on-premises or adjacent premises that are a risk to the development</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -5539,27 +5667,27 @@
       <c r="B104" s="2" t="n"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>falling-trees-document</t>
+          <t>other-contact</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Falling trees document</t>
+          <t>Other site visit contact</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>number</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr"/>
@@ -5568,7 +5696,7 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -5587,33 +5715,41 @@
       <c r="B105" s="2" t="n"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>tree-removal</t>
+          <t>other-contact</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Tree removal</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr"/>
-      <c r="G105" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="H105" s="2" t="inlineStr"/>
       <c r="I105" s="2" t="inlineStr"/>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges need to be pruned or removed</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -5623,8 +5759,16 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n"/>
-      <c r="B106" s="2" t="n"/>
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Trees and hedges information</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>trees-hedges</t>
+        </is>
+      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>Details of trees and/or hedges that will be affected by the proposed development</t>
@@ -5632,39 +5776,167 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>tree-removal-plan</t>
+          <t>has-falling-trees-risk</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Tree removal plan</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Falling trees risk</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr"/>
       <c r="I106" s="2" t="inlineStr"/>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
+          <t>Whether there are falling trees on-premises or adjacent premises that are a risk to the development</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n"/>
+      <c r="B107" s="2" t="n"/>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>falling-trees-document</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Falling trees document</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
           <t>A unique reference for the data item</t>
         </is>
       </c>
-      <c r="M106" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N106" s="2" t="inlineStr">
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n"/>
+      <c r="B108" s="2" t="n"/>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>tree-removal</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Tree removal</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>Whether trees or hedges need to be pruned or removed</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n"/>
+      <c r="B109" s="2" t="n"/>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>tree-removal-plan</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Tree removal plan</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>A unique reference for the data item</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -5672,42 +5944,42 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A36:A39"/>
-    <mergeCell ref="A40:A45"/>
-    <mergeCell ref="B97:B102"/>
-    <mergeCell ref="B78:B82"/>
-    <mergeCell ref="B88:B96"/>
+    <mergeCell ref="B53:B55"/>
+    <mergeCell ref="B49"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A56:A62"/>
+    <mergeCell ref="B100:B105"/>
     <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A103:A106"/>
-    <mergeCell ref="A61:A75"/>
-    <mergeCell ref="B61:B75"/>
-    <mergeCell ref="B83:B87"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="A83:A87"/>
-    <mergeCell ref="B47"/>
-    <mergeCell ref="B46"/>
-    <mergeCell ref="B103:B106"/>
-    <mergeCell ref="B54:B60"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="B106:B109"/>
+    <mergeCell ref="B28:B36"/>
+    <mergeCell ref="A63:A78"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="A48"/>
+    <mergeCell ref="A91:A99"/>
+    <mergeCell ref="A81:A85"/>
+    <mergeCell ref="A49"/>
+    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="B63:B78"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="B48"/>
+    <mergeCell ref="A28:A36"/>
+    <mergeCell ref="B56:B62"/>
+    <mergeCell ref="B81:B85"/>
     <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B41:B47"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="B91:B99"/>
+    <mergeCell ref="A100:A105"/>
     <mergeCell ref="B24:B27"/>
-    <mergeCell ref="B28:B35"/>
-    <mergeCell ref="A54:A60"/>
-    <mergeCell ref="A46"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="B36:B39"/>
-    <mergeCell ref="A97:A102"/>
-    <mergeCell ref="B40:B45"/>
-    <mergeCell ref="A78:A82"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A88:A96"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A106:A109"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="B86:B90"/>
     <mergeCell ref="B20:B23"/>
     <mergeCell ref="B2:B19"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A28:A35"/>
-    <mergeCell ref="A47"/>
+    <mergeCell ref="A86:A90"/>
+    <mergeCell ref="A41:A47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
